--- a/core/static/files/templateSum.xlsx
+++ b/core/static/files/templateSum.xlsx
@@ -9588,7 +9588,7 @@
     <t>Сумма</t>
   </si>
   <si>
-    <t>Заключенно договоров</t>
+    <t>Заключено договоров</t>
   </si>
   <si>
     <t>Оформлено ЗнП</t>
